--- a/Datos Experimentales/Data 24020.xlsx
+++ b/Datos Experimentales/Data 24020.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B61AF8-A6F7-4D96-9520-0AC109744290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1032,11 +1043,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1065,14 +1073,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1397,10 +1414,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1408,7 +1426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1416,7 +1434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1424,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1432,7 +1450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1440,7 +1458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1456,7 +1474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1464,7 +1482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1472,7 +1490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1480,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1488,7 +1506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1496,7 +1514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1504,7 +1522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1512,7 +1530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1520,7 +1538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1528,7 +1546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1536,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1544,7 +1562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1552,7 +1570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1568,7 +1586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1576,7 +1594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1584,7 +1602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1592,7 +1610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1600,7 +1618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1608,7 +1626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1616,7 +1634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1624,7 +1642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1632,7 +1650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1640,7 +1658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1648,7 +1666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1664,7 +1682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1672,7 +1690,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1680,7 +1698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1688,7 +1706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1696,7 +1714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1704,7 +1722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1712,7 +1730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1720,7 +1738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1728,7 +1746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1736,7 +1754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1744,7 +1762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1752,7 +1770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1760,7 +1778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1768,7 +1786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1776,7 +1794,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1784,7 +1802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1792,7 +1810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1800,7 +1818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1808,7 +1826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1816,7 +1834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1824,7 +1842,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1832,7 +1850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1840,7 +1858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1848,7 +1866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1856,7 +1874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1864,7 +1882,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1872,7 +1890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1880,7 +1898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1888,7 +1906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1904,7 +1922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1912,7 +1930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1920,7 +1938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1928,7 +1946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1936,7 +1954,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1944,7 +1962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1952,7 +1970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1960,7 +1978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -1968,7 +1986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -1976,7 +1994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -1984,7 +2002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -1992,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2000,7 +2018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2008,7 +2026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2016,7 +2034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2024,7 +2042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2032,7 +2050,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -2040,7 +2058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2048,7 +2066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2056,7 +2074,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2064,7 +2082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2072,7 +2090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2080,7 +2098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2088,7 +2106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2096,7 +2114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2104,7 +2122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2112,7 +2130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2120,7 +2138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2128,7 +2146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2136,7 +2154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2144,7 +2162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2152,7 +2170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2160,7 +2178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2168,7 +2186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2176,7 +2194,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2184,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2192,7 +2210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2200,7 +2218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2208,7 +2226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2216,7 +2234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2224,7 +2242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2232,7 +2250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2240,7 +2258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2248,7 +2266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2256,7 +2274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2264,7 +2282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2272,7 +2290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2280,7 +2298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2288,7 +2306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2296,7 +2314,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2304,7 +2322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2312,7 +2330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2320,7 +2338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2328,7 +2346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2337,27 +2355,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B117"/>
+    <ignoredError sqref="A1:B117" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>280</v>
       </c>
@@ -2378,17 +2400,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>285</v>
       </c>
@@ -2399,18 +2423,18 @@
         <v>287</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>288</v>
       </c>
       <c r="B2">
-        <v>0.2263888888888889</v>
+        <v>0.22638888888888889</v>
       </c>
       <c r="C2">
         <v>17.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>289</v>
       </c>
@@ -2421,29 +2445,29 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>290</v>
       </c>
       <c r="B4">
-        <v>0.7263888888888889</v>
+        <v>0.72638888888888886</v>
       </c>
       <c r="C4">
         <v>16</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>291</v>
       </c>
       <c r="B5">
-        <v>0.9763888888888889</v>
+        <v>0.97638888888888886</v>
       </c>
       <c r="C5">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>292</v>
       </c>
@@ -2454,7 +2478,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>293</v>
       </c>
@@ -2465,7 +2489,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>294</v>
       </c>
@@ -2476,7 +2500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>295</v>
       </c>
@@ -2487,7 +2511,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>296</v>
       </c>
@@ -2498,7 +2522,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>297</v>
       </c>
@@ -2509,7 +2533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>298</v>
       </c>
@@ -2520,7 +2544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>299</v>
       </c>
@@ -2531,7 +2555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>300</v>
       </c>
@@ -2542,7 +2566,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>301</v>
       </c>
@@ -2553,7 +2577,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>302</v>
       </c>
@@ -2564,7 +2588,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>303</v>
       </c>
@@ -2575,271 +2599,271 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>304</v>
       </c>
       <c r="B18">
-        <v>4.226388888888889</v>
+        <v>4.2263888888888888</v>
       </c>
       <c r="C18">
         <v>16.3</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>305</v>
       </c>
       <c r="B19">
-        <v>4.476388888888889</v>
+        <v>4.4763888888888888</v>
       </c>
       <c r="C19">
-        <v>16.1</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>306</v>
       </c>
       <c r="B20">
-        <v>4.726388888888889</v>
+        <v>4.7263888888888888</v>
       </c>
       <c r="C20">
         <v>16</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>307</v>
       </c>
       <c r="B21">
-        <v>4.976388888888889</v>
+        <v>4.9763888888888888</v>
       </c>
       <c r="C21">
         <v>16.5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>308</v>
       </c>
       <c r="B22">
-        <v>5.226388888888889</v>
+        <v>5.2263888888888888</v>
       </c>
       <c r="C22">
         <v>16.8</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>309</v>
       </c>
       <c r="B23">
-        <v>5.476388888888889</v>
+        <v>5.4763888888888888</v>
       </c>
       <c r="C23">
         <v>16.3</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>310</v>
       </c>
       <c r="B24">
-        <v>5.726388888888889</v>
+        <v>5.7263888888888888</v>
       </c>
       <c r="C24">
         <v>16.5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>311</v>
       </c>
       <c r="B25">
-        <v>5.976388888888889</v>
+        <v>5.9763888888888888</v>
       </c>
       <c r="C25">
         <v>16.5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>312</v>
       </c>
       <c r="B26">
-        <v>6.226388888888889</v>
+        <v>6.2263888888888888</v>
       </c>
       <c r="C26">
         <v>16.8</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>313</v>
       </c>
       <c r="B27">
-        <v>6.476388888888889</v>
+        <v>6.4763888888888888</v>
       </c>
       <c r="C27">
         <v>16.8</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>314</v>
       </c>
       <c r="B28">
-        <v>6.726388888888889</v>
+        <v>6.7263888888888888</v>
       </c>
       <c r="C28">
         <v>16</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>315</v>
       </c>
       <c r="B29">
-        <v>6.976388888888889</v>
+        <v>6.9763888888888888</v>
       </c>
       <c r="C29">
         <v>16</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>316</v>
       </c>
       <c r="B30">
-        <v>7.226388888888889</v>
+        <v>7.2263888888888888</v>
       </c>
       <c r="C30">
         <v>16.3</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>317</v>
       </c>
       <c r="B31">
-        <v>7.476388888888889</v>
+        <v>7.4763888888888888</v>
       </c>
       <c r="C31">
         <v>16.7</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>318</v>
       </c>
       <c r="B32">
-        <v>7.726388888888889</v>
+        <v>7.7263888888888888</v>
       </c>
       <c r="C32">
-        <v>17.4</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>319</v>
       </c>
       <c r="B33">
-        <v>7.976388888888889</v>
+        <v>7.9763888888888888</v>
       </c>
       <c r="C33">
-        <v>17.4</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>320</v>
       </c>
       <c r="B34">
-        <v>8.22638888888889</v>
+        <v>8.2263888888888896</v>
       </c>
       <c r="C34">
-        <v>16.1</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>321</v>
       </c>
       <c r="B35">
-        <v>8.47638888888889</v>
+        <v>8.4763888888888896</v>
       </c>
       <c r="C35">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>322</v>
       </c>
       <c r="B36">
-        <v>8.72638888888889</v>
+        <v>8.7263888888888896</v>
       </c>
       <c r="C36">
         <v>16.5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>323</v>
       </c>
       <c r="B37">
-        <v>8.97638888888889</v>
+        <v>8.9763888888888896</v>
       </c>
       <c r="C37">
         <v>16.2</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>324</v>
       </c>
       <c r="B38">
-        <v>9.22638888888889</v>
+        <v>9.2263888888888896</v>
       </c>
       <c r="C38">
         <v>17.3</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>325</v>
       </c>
       <c r="B39">
-        <v>9.47638888888889</v>
+        <v>9.4763888888888896</v>
       </c>
       <c r="C39">
         <v>16.3</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>326</v>
       </c>
       <c r="B40">
-        <v>9.72638888888889</v>
+        <v>9.7263888888888896</v>
       </c>
       <c r="C40">
         <v>16.8</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>327</v>
       </c>
       <c r="B41">
-        <v>9.97638888888889</v>
+        <v>9.9763888888888896</v>
       </c>
       <c r="C41">
         <v>16.5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>328</v>
       </c>
@@ -2847,10 +2871,10 @@
         <v>10.22638888888889</v>
       </c>
       <c r="C42">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>329</v>
       </c>
@@ -2858,10 +2882,10 @@
         <v>10.47638888888889</v>
       </c>
       <c r="C43">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>330</v>
       </c>
@@ -2872,7 +2896,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>331</v>
       </c>
@@ -2880,21 +2904,23 @@
         <v>10.97638888888889</v>
       </c>
       <c r="C45">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError sqref="A1:C45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>285</v>
       </c>
@@ -2905,18 +2931,18 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>288</v>
       </c>
       <c r="B2">
-        <v>0.2263888888888889</v>
+        <v>0.22638888888888889</v>
       </c>
       <c r="C2">
         <v>1086</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>289</v>
       </c>
@@ -2927,29 +2953,29 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>290</v>
       </c>
       <c r="B4">
-        <v>0.7263888888888889</v>
+        <v>0.72638888888888886</v>
       </c>
       <c r="C4">
         <v>1085</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>291</v>
       </c>
       <c r="B5">
-        <v>0.9763888888888889</v>
+        <v>0.97638888888888886</v>
       </c>
       <c r="C5">
         <v>1084</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>292</v>
       </c>
@@ -2960,7 +2986,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>293</v>
       </c>
@@ -2971,7 +2997,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>294</v>
       </c>
@@ -2982,7 +3008,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>295</v>
       </c>
@@ -2993,7 +3019,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>296</v>
       </c>
@@ -3004,7 +3030,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>297</v>
       </c>
@@ -3015,7 +3041,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>298</v>
       </c>
@@ -3026,7 +3052,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>299</v>
       </c>
@@ -3037,7 +3063,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>300</v>
       </c>
@@ -3048,7 +3074,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>301</v>
       </c>
@@ -3059,7 +3085,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>302</v>
       </c>
@@ -3070,7 +3096,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>303</v>
       </c>
@@ -3081,271 +3107,271 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>304</v>
       </c>
       <c r="B18">
-        <v>4.226388888888889</v>
+        <v>4.2263888888888888</v>
       </c>
       <c r="C18">
         <v>1027</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>305</v>
       </c>
       <c r="B19">
-        <v>4.476388888888889</v>
+        <v>4.4763888888888888</v>
       </c>
       <c r="C19">
         <v>1022</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>306</v>
       </c>
       <c r="B20">
-        <v>4.726388888888889</v>
+        <v>4.7263888888888888</v>
       </c>
       <c r="C20">
         <v>1019</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>307</v>
       </c>
       <c r="B21">
-        <v>4.976388888888889</v>
+        <v>4.9763888888888888</v>
       </c>
       <c r="C21">
         <v>1017</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>308</v>
       </c>
       <c r="B22">
-        <v>5.226388888888889</v>
+        <v>5.2263888888888888</v>
       </c>
       <c r="C22">
         <v>1016</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>309</v>
       </c>
       <c r="B23">
-        <v>5.476388888888889</v>
+        <v>5.4763888888888888</v>
       </c>
       <c r="C23">
         <v>1013</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>310</v>
       </c>
       <c r="B24">
-        <v>5.726388888888889</v>
+        <v>5.7263888888888888</v>
       </c>
       <c r="C24">
         <v>1009</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>311</v>
       </c>
       <c r="B25">
-        <v>5.976388888888889</v>
+        <v>5.9763888888888888</v>
       </c>
       <c r="C25">
         <v>1008</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>312</v>
       </c>
       <c r="B26">
-        <v>6.226388888888889</v>
+        <v>6.2263888888888888</v>
       </c>
       <c r="C26">
         <v>1008</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>313</v>
       </c>
       <c r="B27">
-        <v>6.476388888888889</v>
+        <v>6.4763888888888888</v>
       </c>
       <c r="C27">
         <v>1006</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>314</v>
       </c>
       <c r="B28">
-        <v>6.726388888888889</v>
+        <v>6.7263888888888888</v>
       </c>
       <c r="C28">
         <v>1004</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>315</v>
       </c>
       <c r="B29">
-        <v>6.976388888888889</v>
+        <v>6.9763888888888888</v>
       </c>
       <c r="C29">
         <v>1003</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>316</v>
       </c>
       <c r="B30">
-        <v>7.226388888888889</v>
+        <v>7.2263888888888888</v>
       </c>
       <c r="C30">
         <v>1003</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>317</v>
       </c>
       <c r="B31">
-        <v>7.476388888888889</v>
+        <v>7.4763888888888888</v>
       </c>
       <c r="C31">
         <v>1001</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>318</v>
       </c>
       <c r="B32">
-        <v>7.726388888888889</v>
+        <v>7.7263888888888888</v>
       </c>
       <c r="C32">
         <v>999</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>319</v>
       </c>
       <c r="B33">
-        <v>7.976388888888889</v>
+        <v>7.9763888888888888</v>
       </c>
       <c r="C33">
         <v>999</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>320</v>
       </c>
       <c r="B34">
-        <v>8.22638888888889</v>
+        <v>8.2263888888888896</v>
       </c>
       <c r="C34">
         <v>999</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>321</v>
       </c>
       <c r="B35">
-        <v>8.47638888888889</v>
+        <v>8.4763888888888896</v>
       </c>
       <c r="C35">
         <v>998</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>322</v>
       </c>
       <c r="B36">
-        <v>8.72638888888889</v>
+        <v>8.7263888888888896</v>
       </c>
       <c r="C36">
         <v>998</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>323</v>
       </c>
       <c r="B37">
-        <v>8.97638888888889</v>
+        <v>8.9763888888888896</v>
       </c>
       <c r="C37">
         <v>997</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>324</v>
       </c>
       <c r="B38">
-        <v>9.22638888888889</v>
+        <v>9.2263888888888896</v>
       </c>
       <c r="C38">
         <v>997</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>325</v>
       </c>
       <c r="B39">
-        <v>9.47638888888889</v>
+        <v>9.4763888888888896</v>
       </c>
       <c r="C39">
         <v>995</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>326</v>
       </c>
       <c r="B40">
-        <v>9.72638888888889</v>
+        <v>9.7263888888888896</v>
       </c>
       <c r="C40">
         <v>994</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>327</v>
       </c>
       <c r="B41">
-        <v>9.97638888888889</v>
+        <v>9.9763888888888896</v>
       </c>
       <c r="C41">
         <v>995</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>328</v>
       </c>
@@ -3356,7 +3382,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>329</v>
       </c>
@@ -3367,7 +3393,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>330</v>
       </c>
@@ -3378,7 +3404,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>331</v>
       </c>
@@ -3390,17 +3416,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError sqref="A1:C45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>285</v>
       </c>
@@ -3424,17 +3452,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3748,7 +3778,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9840</v>
       </c>
@@ -3783,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45373.64861111111</v>
+        <v>45373.648611111108</v>
       </c>
       <c r="M2" t="s">
         <v>135</v>
@@ -3792,7 +3822,7 @@
         <v>136</v>
       </c>
       <c r="O2">
-        <v>45380.64861111111</v>
+        <v>45380.648611111108</v>
       </c>
       <c r="P2" t="s">
         <v>137</v>
@@ -3873,7 +3903,7 @@
         <v>145</v>
       </c>
       <c r="AS2">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="AT2">
         <v>11.6</v>
@@ -3972,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="BZ2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -4014,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="CN2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -4042,17 +4072,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CZ2"/>
+    <ignoredError sqref="A1:CZ2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4105,7 +4137,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9840</v>
       </c>
@@ -4134,7 +4166,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9840</v>
       </c>
@@ -4169,7 +4201,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9840</v>
       </c>
@@ -4198,7 +4230,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9840</v>
       </c>
@@ -4212,7 +4244,7 @@
         <v>187</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>183</v>
@@ -4248,7 +4280,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9840</v>
       </c>
@@ -4262,7 +4294,7 @@
         <v>187</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>183</v>
@@ -4298,7 +4330,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9840</v>
       </c>
@@ -4333,7 +4365,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9840</v>
       </c>
@@ -4380,7 +4412,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9840</v>
       </c>
@@ -4409,7 +4441,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9840</v>
       </c>
@@ -4444,7 +4476,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9840</v>
       </c>
@@ -4479,7 +4511,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9840</v>
       </c>
@@ -4515,17 +4547,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4557,7 +4591,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9840</v>
       </c>
@@ -4589,7 +4623,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9840</v>
       </c>
@@ -4621,7 +4655,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9840</v>
       </c>
@@ -4654,27 +4688,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4706,7 +4744,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9840</v>
       </c>
@@ -4739,17 +4777,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4766,7 +4806,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9840</v>
       </c>
@@ -4778,27 +4818,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4848,7 +4892,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9840</v>
       </c>
@@ -4861,7 +4905,7 @@
       <c r="D2">
         <v>6814</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.774722222224</v>
       </c>
       <c r="F2" t="s">
@@ -4892,13 +4936,13 @@
         <v>245</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9840</v>
       </c>
@@ -4911,7 +4955,7 @@
       <c r="D3">
         <v>6814</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.774722222224</v>
       </c>
       <c r="F3" t="s">
@@ -4942,13 +4986,13 @@
         <v>245</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9840</v>
       </c>
@@ -4961,7 +5005,7 @@
       <c r="D4">
         <v>6814</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.774722222224</v>
       </c>
       <c r="F4" t="s">
@@ -4998,7 +5042,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9840</v>
       </c>
@@ -5011,7 +5055,7 @@
       <c r="D5">
         <v>6814</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.774722222224</v>
       </c>
       <c r="F5" t="s">
@@ -5048,7 +5092,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9840</v>
       </c>
@@ -5061,7 +5105,7 @@
       <c r="D6">
         <v>6814</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.774722222224</v>
       </c>
       <c r="F6" t="s">
@@ -5098,7 +5142,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9840</v>
       </c>
@@ -5111,7 +5155,7 @@
       <c r="D7">
         <v>6814</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.774722222224</v>
       </c>
       <c r="F7" t="s">
@@ -5148,7 +5192,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9840</v>
       </c>
@@ -5161,7 +5205,7 @@
       <c r="D8">
         <v>6814</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.774722222224</v>
       </c>
       <c r="F8" t="s">
@@ -5198,7 +5242,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9840</v>
       </c>
@@ -5211,8 +5255,8 @@
       <c r="D9">
         <v>6881</v>
       </c>
-      <c r="E9">
-        <v>45376.656793981485</v>
+      <c r="E9" s="1">
+        <v>45373.656793981485</v>
       </c>
       <c r="F9" t="s">
         <v>134</v>
@@ -5242,13 +5286,13 @@
         <v>245</v>
       </c>
       <c r="O9">
-        <v>7.9254</v>
+        <v>7.9253999999999998</v>
       </c>
       <c r="P9" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9840</v>
       </c>
@@ -5261,8 +5305,8 @@
       <c r="D10">
         <v>6881</v>
       </c>
-      <c r="E10">
-        <v>45376.656793981485</v>
+      <c r="E10" s="1">
+        <v>45373.656793981485</v>
       </c>
       <c r="F10" t="s">
         <v>134</v>
@@ -5298,7 +5342,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9840</v>
       </c>
@@ -5311,8 +5355,8 @@
       <c r="D11">
         <v>6881</v>
       </c>
-      <c r="E11">
-        <v>45376.656793981485</v>
+      <c r="E11" s="1">
+        <v>45373.656793981485</v>
       </c>
       <c r="F11" t="s">
         <v>134</v>
@@ -5342,13 +5386,13 @@
         <v>245</v>
       </c>
       <c r="O11">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="P11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9840</v>
       </c>
@@ -5361,8 +5405,8 @@
       <c r="D12">
         <v>6881</v>
       </c>
-      <c r="E12">
-        <v>45376.656793981485</v>
+      <c r="E12" s="1">
+        <v>45373.656793981485</v>
       </c>
       <c r="F12" t="s">
         <v>134</v>
@@ -5398,7 +5442,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9840</v>
       </c>
@@ -5411,8 +5455,8 @@
       <c r="D13">
         <v>6881</v>
       </c>
-      <c r="E13">
-        <v>45376.656793981485</v>
+      <c r="E13" s="1">
+        <v>45373.656793981485</v>
       </c>
       <c r="F13" t="s">
         <v>134</v>
@@ -5448,7 +5492,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9840</v>
       </c>
@@ -5461,8 +5505,8 @@
       <c r="D14">
         <v>6881</v>
       </c>
-      <c r="E14">
-        <v>45376.656793981485</v>
+      <c r="E14" s="1">
+        <v>45373.656793981485</v>
       </c>
       <c r="F14" t="s">
         <v>134</v>
@@ -5498,7 +5542,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9840</v>
       </c>
@@ -5511,8 +5555,8 @@
       <c r="D15">
         <v>6881</v>
       </c>
-      <c r="E15">
-        <v>45376.656793981485</v>
+      <c r="E15" s="1">
+        <v>45373.656793981485</v>
       </c>
       <c r="F15" t="s">
         <v>134</v>
@@ -5548,7 +5592,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9840</v>
       </c>
@@ -5561,8 +5605,8 @@
       <c r="D16">
         <v>7098</v>
       </c>
-      <c r="E16">
-        <v>45383.62278935185</v>
+      <c r="E16" s="1">
+        <v>45383.622789351852</v>
       </c>
       <c r="F16" t="s">
         <v>134</v>
@@ -5598,7 +5642,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9840</v>
       </c>
@@ -5611,8 +5655,8 @@
       <c r="D17">
         <v>7163</v>
       </c>
-      <c r="E17">
-        <v>45384.85159722222</v>
+      <c r="E17" s="1">
+        <v>45384.851597222223</v>
       </c>
       <c r="F17" t="s">
         <v>134</v>
@@ -5648,7 +5692,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9840</v>
       </c>
@@ -5661,7 +5705,7 @@
       <c r="D18">
         <v>7246</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F18" t="s">
@@ -5698,7 +5742,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9840</v>
       </c>
@@ -5711,7 +5755,7 @@
       <c r="D19">
         <v>7246</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F19" t="s">
@@ -5742,13 +5786,13 @@
         <v>245</v>
       </c>
       <c r="O19">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="P19" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9840</v>
       </c>
@@ -5761,7 +5805,7 @@
       <c r="D20">
         <v>7246</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F20" t="s">
@@ -5798,7 +5842,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9840</v>
       </c>
@@ -5811,7 +5855,7 @@
       <c r="D21">
         <v>7246</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F21" t="s">
@@ -5848,7 +5892,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9840</v>
       </c>
@@ -5861,7 +5905,7 @@
       <c r="D22">
         <v>7246</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F22" t="s">
@@ -5898,7 +5942,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9840</v>
       </c>
@@ -5911,7 +5955,7 @@
       <c r="D23">
         <v>7246</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F23" t="s">
@@ -5942,13 +5986,13 @@
         <v>245</v>
       </c>
       <c r="O23">
-        <v>0.179</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="P23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9840</v>
       </c>
@@ -5961,7 +6005,7 @@
       <c r="D24">
         <v>7246</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F24" t="s">
@@ -5998,7 +6042,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9840</v>
       </c>
@@ -6011,7 +6055,7 @@
       <c r="D25">
         <v>7246</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F25" t="s">
@@ -6048,7 +6092,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9840</v>
       </c>
@@ -6061,7 +6105,7 @@
       <c r="D26">
         <v>7246</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>45386.8675</v>
       </c>
       <c r="F26" t="s">
@@ -6098,7 +6142,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9840</v>
       </c>
@@ -6111,7 +6155,7 @@
       <c r="D27">
         <v>7417</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F27" t="s">
@@ -6142,13 +6186,13 @@
         <v>245</v>
       </c>
       <c r="O27">
-        <v>5.11</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="P27" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9840</v>
       </c>
@@ -6161,7 +6205,7 @@
       <c r="D28">
         <v>7417</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F28" t="s">
@@ -6192,13 +6236,13 @@
         <v>245</v>
       </c>
       <c r="O28">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="P28" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9840</v>
       </c>
@@ -6211,7 +6255,7 @@
       <c r="D29">
         <v>7417</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F29" t="s">
@@ -6248,7 +6292,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9840</v>
       </c>
@@ -6261,7 +6305,7 @@
       <c r="D30">
         <v>7417</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F30" t="s">
@@ -6298,7 +6342,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9840</v>
       </c>
@@ -6311,7 +6355,7 @@
       <c r="D31">
         <v>7417</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F31" t="s">
@@ -6342,13 +6386,13 @@
         <v>245</v>
       </c>
       <c r="O31">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="P31" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9840</v>
       </c>
@@ -6361,7 +6405,7 @@
       <c r="D32">
         <v>7417</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F32" t="s">
@@ -6398,7 +6442,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9840</v>
       </c>
@@ -6411,7 +6455,7 @@
       <c r="D33">
         <v>7417</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F33" t="s">
@@ -6442,13 +6486,13 @@
         <v>245</v>
       </c>
       <c r="O33">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="P33" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9840</v>
       </c>
@@ -6461,7 +6505,7 @@
       <c r="D34">
         <v>7417</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F34" t="s">
@@ -6498,7 +6542,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9840</v>
       </c>
@@ -6511,7 +6555,7 @@
       <c r="D35">
         <v>7417</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F35" t="s">
@@ -6548,7 +6592,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9840</v>
       </c>
@@ -6561,7 +6605,7 @@
       <c r="D36">
         <v>7417</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="1">
         <v>45391.684120370366</v>
       </c>
       <c r="F36" t="s">
@@ -6598,7 +6642,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9840</v>
       </c>
@@ -6611,8 +6655,8 @@
       <c r="D37">
         <v>7427</v>
       </c>
-      <c r="E37">
-        <v>45391.84416666666</v>
+      <c r="E37" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F37" t="s">
         <v>134</v>
@@ -6642,13 +6686,13 @@
         <v>245</v>
       </c>
       <c r="O37">
-        <v>5.11</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="P37" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9840</v>
       </c>
@@ -6661,8 +6705,8 @@
       <c r="D38">
         <v>7427</v>
       </c>
-      <c r="E38">
-        <v>45391.84416666666</v>
+      <c r="E38" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F38" t="s">
         <v>134</v>
@@ -6692,13 +6736,13 @@
         <v>245</v>
       </c>
       <c r="O38">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="P38" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9840</v>
       </c>
@@ -6711,8 +6755,8 @@
       <c r="D39">
         <v>7427</v>
       </c>
-      <c r="E39">
-        <v>45391.84416666666</v>
+      <c r="E39" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F39" t="s">
         <v>134</v>
@@ -6748,7 +6792,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>9840</v>
       </c>
@@ -6761,8 +6805,8 @@
       <c r="D40">
         <v>7427</v>
       </c>
-      <c r="E40">
-        <v>45391.84416666666</v>
+      <c r="E40" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F40" t="s">
         <v>134</v>
@@ -6798,7 +6842,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9840</v>
       </c>
@@ -6811,8 +6855,8 @@
       <c r="D41">
         <v>7427</v>
       </c>
-      <c r="E41">
-        <v>45391.84416666666</v>
+      <c r="E41" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F41" t="s">
         <v>134</v>
@@ -6842,13 +6886,13 @@
         <v>245</v>
       </c>
       <c r="O41">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="P41" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9840</v>
       </c>
@@ -6861,8 +6905,8 @@
       <c r="D42">
         <v>7427</v>
       </c>
-      <c r="E42">
-        <v>45391.84416666666</v>
+      <c r="E42" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F42" t="s">
         <v>134</v>
@@ -6898,7 +6942,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>9840</v>
       </c>
@@ -6911,8 +6955,8 @@
       <c r="D43">
         <v>7427</v>
       </c>
-      <c r="E43">
-        <v>45391.84416666666</v>
+      <c r="E43" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F43" t="s">
         <v>134</v>
@@ -6942,13 +6986,13 @@
         <v>245</v>
       </c>
       <c r="O43">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="P43" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>9840</v>
       </c>
@@ -6961,8 +7005,8 @@
       <c r="D44">
         <v>7427</v>
       </c>
-      <c r="E44">
-        <v>45391.84416666666</v>
+      <c r="E44" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F44" t="s">
         <v>134</v>
@@ -6998,7 +7042,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>9840</v>
       </c>
@@ -7011,8 +7055,8 @@
       <c r="D45">
         <v>7427</v>
       </c>
-      <c r="E45">
-        <v>45391.84416666666</v>
+      <c r="E45" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F45" t="s">
         <v>134</v>
@@ -7048,7 +7092,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9840</v>
       </c>
@@ -7061,8 +7105,8 @@
       <c r="D46">
         <v>7427</v>
       </c>
-      <c r="E46">
-        <v>45391.84416666666</v>
+      <c r="E46" s="1">
+        <v>45391.844166666662</v>
       </c>
       <c r="F46" t="s">
         <v>134</v>
@@ -7099,8 +7143,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P46"/>
+    <ignoredError sqref="A1:P8 A16:P46 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>